--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-26) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-26) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83075,7 +83075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
         </is>
       </c>
     </row>
@@ -84499,7 +84499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
         </is>
       </c>
     </row>
@@ -85816,7 +85816,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-06-28 (actualización 2026-06-26).</t>
+          <t>datos al 2026-06-28 (actualización 2026-06-27).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83075,7 +83075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
         </is>
       </c>
     </row>
@@ -84499,7 +84499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-27)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
         </is>
       </c>
     </row>
@@ -85816,7 +85816,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-06-28 (actualización 2026-06-27).</t>
+          <t>datos al 2026-06-28 (actualización 2026-06-28).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-29)</t>
         </is>
       </c>
     </row>
@@ -4098,7 +4098,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-29) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4267,7 +4267,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-29)</t>
         </is>
       </c>
     </row>
@@ -6204,7 +6204,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-29) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83075,7 +83075,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-29)</t>
         </is>
       </c>
     </row>
@@ -84499,7 +84499,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-28)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-06-28 (actualización 2026-06-29)</t>
         </is>
       </c>
     </row>
@@ -85816,7 +85816,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-06-28 (actualización 2026-06-28).</t>
+          <t>datos al 2026-06-28 (actualización 2026-06-29).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-04) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-04) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83273,7 +83273,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
         </is>
       </c>
     </row>
@@ -84709,7 +84709,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
         </is>
       </c>
     </row>
@@ -86037,7 +86037,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-05 (actualización 2026-07-04).</t>
+          <t>datos al 2026-07-05 (actualización 2026-07-05).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-06) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-06) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83273,7 +83273,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -84709,7 +84709,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-05 (actualización 2026-07-06)</t>
         </is>
       </c>
     </row>
@@ -86037,7 +86037,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-05 (actualización 2026-07-05).</t>
+          <t>datos al 2026-07-05 (actualización 2026-07-06).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-11)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-11) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-11)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-11) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83434,7 +83434,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-11)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
         </is>
       </c>
     </row>
@@ -84870,7 +84870,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-11)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
         </is>
       </c>
     </row>
@@ -86198,7 +86198,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-12 (actualización 2026-07-11).</t>
+          <t>datos al 2026-07-12 (actualización 2026-07-12).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-13)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-13) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-13)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-13) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83434,7 +83434,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-13)</t>
         </is>
       </c>
     </row>
@@ -84870,7 +84870,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-12)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-12 (actualización 2026-07-13)</t>
         </is>
       </c>
     </row>
@@ -86198,7 +86198,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-12 (actualización 2026-07-12).</t>
+          <t>datos al 2026-07-12 (actualización 2026-07-13).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-18)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-18) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-18)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-18) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83595,7 +83595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-18)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
         </is>
       </c>
     </row>
@@ -85031,7 +85031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-18)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
         </is>
       </c>
     </row>
@@ -86359,7 +86359,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-19 (actualización 2026-07-18).</t>
+          <t>datos al 2026-07-19 (actualización 2026-07-19).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-20)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-20) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-20)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-20) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83595,7 +83595,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-20)</t>
         </is>
       </c>
     </row>
@@ -85031,7 +85031,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-19)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-19 (actualización 2026-07-20)</t>
         </is>
       </c>
     </row>
@@ -86359,7 +86359,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-19 (actualización 2026-07-19).</t>
+          <t>datos al 2026-07-19 (actualización 2026-07-20).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-25)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-25) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-25)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-25) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83756,7 +83756,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-25)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -85192,7 +85192,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-25)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
         </is>
       </c>
     </row>
@@ -86520,7 +86520,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-26 (actualización 2026-07-25).</t>
+          <t>datos al 2026-07-26 (actualización 2026-07-26).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-27)</t>
         </is>
       </c>
     </row>
@@ -4120,7 +4120,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-27) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4290,7 +4290,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-27)</t>
         </is>
       </c>
     </row>
@@ -6240,7 +6240,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-27) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -83756,7 +83756,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-27)</t>
         </is>
       </c>
     </row>
@@ -85192,7 +85192,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-26)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-07-26 (actualización 2026-07-27)</t>
         </is>
       </c>
     </row>
@@ -86520,7 +86520,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-07-26 (actualización 2026-07-26).</t>
+          <t>datos al 2026-07-26 (actualización 2026-07-27).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-01)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-01) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-01)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-01) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84046,7 +84046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-01)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
         </is>
       </c>
     </row>
@@ -85494,7 +85494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-01)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
         </is>
       </c>
     </row>
@@ -86833,7 +86833,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-06 (actualización 2026-08-01).</t>
+          <t>datos al 2026-08-06 (actualización 2026-08-02).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84046,7 +84046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
         </is>
       </c>
     </row>
@@ -85494,7 +85494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-02)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
         </is>
       </c>
     </row>
@@ -86833,7 +86833,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-06 (actualización 2026-08-02).</t>
+          <t>datos al 2026-08-06 (actualización 2026-08-03).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84046,7 +84046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
         </is>
       </c>
     </row>
@@ -85494,7 +85494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-03)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
         </is>
       </c>
     </row>
@@ -86833,7 +86833,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-06 (actualización 2026-08-03).</t>
+          <t>datos al 2026-08-06 (actualización 2026-08-04).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84046,7 +84046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
         </is>
       </c>
     </row>
@@ -85494,7 +85494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-04)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
         </is>
       </c>
     </row>
@@ -86833,7 +86833,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-06 (actualización 2026-08-04).</t>
+          <t>datos al 2026-08-06 (actualización 2026-08-05).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84046,7 +84046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
         </is>
       </c>
     </row>
@@ -85494,7 +85494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
         </is>
       </c>
     </row>
@@ -86833,7 +86833,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-06 (actualización 2026-08-05).</t>
+          <t>datos al 2026-08-06 (actualización 2026-08-06).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-07)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-07) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-07)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-07) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84046,7 +84046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-07)</t>
         </is>
       </c>
     </row>
@@ -85494,7 +85494,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-06 (actualización 2026-08-07)</t>
         </is>
       </c>
     </row>
@@ -86833,7 +86833,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-06 (actualización 2026-08-06).</t>
+          <t>datos al 2026-08-06 (actualización 2026-08-07).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-08)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-08) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-08)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-08) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84115,7 +84115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-08)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
         </is>
       </c>
     </row>
@@ -85563,7 +85563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-08)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
         </is>
       </c>
     </row>
@@ -86902,7 +86902,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-09 (actualización 2026-08-08).</t>
+          <t>datos al 2026-08-09 (actualización 2026-08-09).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-10)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-10) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-10)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-10) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84115,7 +84115,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-10)</t>
         </is>
       </c>
     </row>
@@ -85563,7 +85563,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-09)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-09 (actualización 2026-08-10)</t>
         </is>
       </c>
     </row>
@@ -86902,7 +86902,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-09 (actualización 2026-08-09).</t>
+          <t>datos al 2026-08-09 (actualización 2026-08-10).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-15)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-15) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-15)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-15) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84276,7 +84276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-15)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -85724,7 +85724,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-15)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
         </is>
       </c>
     </row>
@@ -87063,7 +87063,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-16 (actualización 2026-08-15).</t>
+          <t>datos al 2026-08-16 (actualización 2026-08-16).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-17)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-17) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-17)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-17) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84276,7 +84276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-17)</t>
         </is>
       </c>
     </row>
@@ -85724,7 +85724,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-16)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-16 (actualización 2026-08-17)</t>
         </is>
       </c>
     </row>
@@ -87063,7 +87063,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-16 (actualización 2026-08-16).</t>
+          <t>datos al 2026-08-16 (actualización 2026-08-17).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-22)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-22) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-22)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-22) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84437,7 +84437,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-22)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
         </is>
       </c>
     </row>
@@ -85885,7 +85885,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-22)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
         </is>
       </c>
     </row>
@@ -87224,7 +87224,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-23 (actualización 2026-08-22).</t>
+          <t>datos al 2026-08-23 (actualización 2026-08-23).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-24) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-24) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84437,7 +84437,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -85885,7 +85885,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-23)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-23 (actualización 2026-08-24)</t>
         </is>
       </c>
     </row>
@@ -87224,7 +87224,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-23 (actualización 2026-08-23).</t>
+          <t>datos al 2026-08-23 (actualización 2026-08-24).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-29)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-29) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-29)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-29) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84598,7 +84598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-29)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
         </is>
       </c>
     </row>
@@ -86046,7 +86046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-29)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
         </is>
       </c>
     </row>
@@ -87385,7 +87385,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-30 (actualización 2026-08-29).</t>
+          <t>datos al 2026-08-30 (actualización 2026-08-30).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-31)</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-31) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-31)</t>
         </is>
       </c>
     </row>
@@ -6276,7 +6276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-31) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84598,7 +84598,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-31)</t>
         </is>
       </c>
     </row>
@@ -86046,7 +86046,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-30)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-08-30 (actualización 2026-08-31)</t>
         </is>
       </c>
     </row>
@@ -87385,7 +87385,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-08-30 (actualización 2026-08-30).</t>
+          <t>datos al 2026-08-30 (actualización 2026-08-31).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-05) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-05) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84796,7 +84796,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
         </is>
       </c>
     </row>
@@ -86256,7 +86256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-05)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
         </is>
       </c>
     </row>
@@ -87606,7 +87606,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-09-06 (actualización 2026-09-05).</t>
+          <t>datos al 2026-09-06 (actualización 2026-09-06).</t>
         </is>
       </c>
     </row>

--- a/sgb.xlsx
+++ b/sgb.xlsx
@@ -1276,7 +1276,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -4164,7 +4164,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-07) | una gráfica por fondo · cada una con su propio eje · se actualizan solas al crecer meses/días</t>
         </is>
       </c>
     </row>
@@ -4336,7 +4336,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -6312,7 +6312,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-07) | una fila por día · lo más reciente arriba · se actualiza a diario</t>
         </is>
       </c>
     </row>
@@ -84796,7 +84796,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -86256,7 +86256,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-06)</t>
+          <t>Grupo SGB (Servicios Generales Bursátiles) | Fuente: sgbfondosdeinversion.com (histórico CSV) | datos al 2026-09-06 (actualización 2026-09-07)</t>
         </is>
       </c>
     </row>
@@ -87606,7 +87606,7 @@
     <row r="4">
       <c r="A4" s="26" t="inlineStr">
         <is>
-          <t>datos al 2026-09-06 (actualización 2026-09-06).</t>
+          <t>datos al 2026-09-06 (actualización 2026-09-07).</t>
         </is>
       </c>
     </row>
